--- a/Course_Materials/SeaLabMOS_Two-Week_Intensive.xlsx
+++ b/Course_Materials/SeaLabMOS_Two-Week_Intensive.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sscop\Desktop\scopazpriv\SeaLabCTDv2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sscop\Desktop\SeaLabCTD\Course_Materials\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{63E229C6-B468-4442-A4E9-A2E65299853A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A3B6C4C-85DC-40D8-B91E-0BCB7AD48986}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" xr2:uid="{0485C282-2A62-4EC2-AFDA-B0527E114407}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="35">
   <si>
     <t>Week</t>
   </si>
@@ -101,12 +101,6 @@
     <t>Prep housing</t>
   </si>
   <si>
-    <t>Assemble into housing, test over weekend</t>
-  </si>
-  <si>
-    <t>H2O ice dunk, plot test data, response time of sensors</t>
-  </si>
-  <si>
     <t>Catch up time</t>
   </si>
   <si>
@@ -138,13 +132,22 @@
   </si>
   <si>
     <t>Test / quiz / questions to answer</t>
+  </si>
+  <si>
+    <t>Assemble into housing, bench test over weekend</t>
+  </si>
+  <si>
+    <t>Slicing multi-day test to only plot response time test</t>
+  </si>
+  <si>
+    <t>Ice water dunk for response time of sensors</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -153,22 +156,26 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -181,8 +188,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -205,27 +218,58 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -561,13 +605,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70C3E5FF-2756-4AE2-B65A-846B739C90FB}">
   <dimension ref="A1:D32"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="9.453125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="61.7265625" customWidth="1"/>
+    <col min="1" max="2" width="8.7265625" style="2"/>
+    <col min="3" max="3" width="11.6328125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="60.26953125" style="2" customWidth="1"/>
+    <col min="5" max="16384" width="8.7265625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -577,332 +623,335 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" s="2">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="3">
         <v>1</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2" s="3">
         <v>1</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="3" t="s">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="5" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4" s="6" t="s">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="3"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="3"/>
+      <c r="B5" s="3">
         <v>2</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="3" t="s">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="3"/>
+      <c r="B6" s="3"/>
+      <c r="C6" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D7" s="6"/>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="3"/>
+      <c r="B7" s="3"/>
+      <c r="C7" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D7" s="8"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="3"/>
+      <c r="B8" s="3">
         <v>3</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="5" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="3" t="s">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" s="3"/>
+      <c r="B9" s="3"/>
+      <c r="C9" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D10" s="6" t="s">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" s="3"/>
+      <c r="B10" s="3"/>
+      <c r="C10" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D10" s="5" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" s="3"/>
+      <c r="B11" s="3">
         <v>4</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D11" s="6"/>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2"/>
-      <c r="C12" s="3" t="s">
+      <c r="D11" s="8"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" s="3"/>
+      <c r="B12" s="3"/>
+      <c r="C12" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="D12" s="5" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D13" s="6" t="s">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" s="3"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D13" s="5" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2">
-        <v>5</v>
-      </c>
-      <c r="C14" s="3" t="s">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" s="3"/>
+      <c r="B14" s="3">
+        <v>5</v>
+      </c>
+      <c r="C14" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D14" s="6" t="s">
+      <c r="D14" s="5" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A15" s="2"/>
-      <c r="B15" s="2"/>
-      <c r="C15" s="3" t="s">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" s="3"/>
+      <c r="B15" s="3"/>
+      <c r="C15" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="D15" s="5" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A16" s="2"/>
-      <c r="B16" s="2"/>
-      <c r="C16" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D16" s="6" t="s">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" s="3"/>
+      <c r="B16" s="3"/>
+      <c r="C16" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" s="7" customFormat="1" ht="5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="6"/>
+      <c r="B17" s="6"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" s="3">
+        <v>2</v>
+      </c>
+      <c r="B18" s="3">
+        <v>6</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" s="3"/>
+      <c r="B19" s="3"/>
+      <c r="C19" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" s="3"/>
+      <c r="B20" s="3"/>
+      <c r="C20" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D20" s="8"/>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" s="3"/>
+      <c r="B21" s="3">
+        <v>7</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D21" s="9" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="17" spans="1:4" s="7" customFormat="1" ht="5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="4"/>
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A18" s="2">
-        <v>2</v>
-      </c>
-      <c r="B18" s="2">
-        <v>6</v>
-      </c>
-      <c r="C18" s="3" t="s">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" s="3"/>
+      <c r="B22" s="3"/>
+      <c r="C22" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D22" s="10"/>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" s="3"/>
+      <c r="B23" s="3"/>
+      <c r="C23" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" s="3"/>
+      <c r="B24" s="3">
+        <v>8</v>
+      </c>
+      <c r="C24" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D18" s="6" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="3" t="s">
+      <c r="D24" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A25" s="3"/>
+      <c r="B25" s="3"/>
+      <c r="C25" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D19" s="6"/>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A20" s="2"/>
-      <c r="B20" s="2"/>
-      <c r="C20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D20" s="6"/>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A21" s="2"/>
-      <c r="B21" s="2">
-        <v>7</v>
-      </c>
-      <c r="C21" s="3" t="s">
+      <c r="D25" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A26" s="3"/>
+      <c r="B26" s="3"/>
+      <c r="C26" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A27" s="3"/>
+      <c r="B27" s="3">
+        <v>9</v>
+      </c>
+      <c r="C27" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D21" s="6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A22" s="2"/>
-      <c r="B22" s="2"/>
-      <c r="C22" s="3" t="s">
+      <c r="D27" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A28" s="3"/>
+      <c r="B28" s="3"/>
+      <c r="C28" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D22" s="6"/>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A23" s="2"/>
-      <c r="B23" s="2"/>
-      <c r="C23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D23" s="6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A24" s="2"/>
-      <c r="B24" s="2">
-        <v>8</v>
-      </c>
-      <c r="C24" s="3" t="s">
+      <c r="D28" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A29" s="3"/>
+      <c r="B29" s="3"/>
+      <c r="C29" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A30" s="3"/>
+      <c r="B30" s="3">
+        <v>10</v>
+      </c>
+      <c r="C30" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D24" s="6" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A25" s="2"/>
-      <c r="B25" s="2"/>
-      <c r="C25" s="3" t="s">
+      <c r="D30" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A31" s="3"/>
+      <c r="B31" s="3"/>
+      <c r="C31" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D25" s="6" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A26" s="2"/>
-      <c r="B26" s="2"/>
-      <c r="C26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D26" s="6" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A27" s="2"/>
-      <c r="B27" s="2">
-        <v>9</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D27" s="6" t="s">
+      <c r="D31" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A32" s="3"/>
+      <c r="B32" s="3"/>
+      <c r="C32" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D32" s="5" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A28" s="2"/>
-      <c r="B28" s="2"/>
-      <c r="C28" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D28" s="6" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A29" s="2"/>
-      <c r="B29" s="2"/>
-      <c r="C29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D29" s="6" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A30" s="2"/>
-      <c r="B30" s="2">
-        <v>10</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D30" s="6" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A31" s="2"/>
-      <c r="B31" s="2"/>
-      <c r="C31" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D31" s="6" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A32" s="2"/>
-      <c r="B32" s="2"/>
-      <c r="C32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D32" s="6" t="s">
-        <v>28</v>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="13">
+    <mergeCell ref="D21:D22"/>
     <mergeCell ref="B21:B23"/>
     <mergeCell ref="B24:B26"/>
     <mergeCell ref="B27:B29"/>
